--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/ekipman_tablosu.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/ekipman_tablosu.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -749,7 +749,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>2,9 m³/sa @ 5,9 mSS</t>
+          <t>3,2 m³/sa @ 5,9 mSS</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 disk / ünite </t>
+          <t xml:space="preserve">112 disk / ünite </t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 752,4 m²</t>
+          <t xml:space="preserve"> 739,2 m²</t>
         </is>
       </c>
     </row>
@@ -990,445 +990,436 @@
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="9" t="inlineStr">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>Redüktör İmalatçısı</t>
         </is>
       </c>
-      <c r="B44" s="10" t="inlineStr">
+      <c r="B44" s="8" t="inlineStr">
         <is>
           <t>PGR veya muadili</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Blower</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve"> 1 Adet</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="18" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>Kapasite</t>
         </is>
       </c>
-      <c r="B48" s="10" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>15 m³/sa @ 200 mbar</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>LS 15 Lamella Seperatör Son Çöktürme Tankı</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="n"/>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>LS 30 Lamella Seperatör Son Çöktürme Tankı</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>İmalat Malzemesi</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>Fiber Gövde &amp; Toz Boyalı Karbon Çelik Şase</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>Miktar</t>
+          <t>Lamella Plaka Alanı</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1 Adet</t>
+          <t>30 m²/tank</t>
         </is>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>İmalat Malzemesi</t>
+          <t>Tank Hacmi</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Fiber Gövde &amp; Toz Boyalı Karbon Çelik Şase</t>
+          <t>3 m³/tank</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>Lamella Plaka Alanı</t>
+          <t>İmalatçı</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>15 m²/tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="18" customHeight="1">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Tank Hacmi</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>2 m³/tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="18" customHeight="1">
-      <c r="A55" s="5" t="inlineStr">
+          <t>PlanetTEK Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Temizleme</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Alta biriken çamur otomatik olarak çamur pompası aracılığı ile çekilir. Gerektiğinde lamella yüzeyleri basınçlı su ile manuel olarak yıkanır.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Son Çöktürme Tankı Çamur Pompası</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 1 Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>İmalatçı</t>
         </is>
       </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>PlanetTEK Inc.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="9" t="inlineStr">
-        <is>
-          <t>Temizleme</t>
-        </is>
-      </c>
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>Alta biriken çamur otomatik olarak çamur pompası aracılığı ile çekilir. Gerektiğinde lamella yüzeyleri basınçlı su ile manuel olarak yıkanır.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
-        <is>
-          <t>Son Çöktürme Tankı Çamur Pompası</t>
-        </is>
-      </c>
-      <c r="B58" s="4" t="n"/>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t>Sumak veya Muadili</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="18" customHeight="1">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>Miktar</t>
+          <t>Kapasite</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1 Adet</t>
+          <t>10 m³/saat @ 8,1 mSS</t>
         </is>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>İmalatçı</t>
+          <t>Motor</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Sumak veya Muadili</t>
+          <t>0.8 kW</t>
         </is>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="A61" s="5" t="inlineStr">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>Tip</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Santrifüj Tip</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>İNŞAAT İŞLERİ</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Izgara Kanalı</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="n"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Miktar</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="inlineStr">
+        <is>
+          <t>1 Adet</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
         <is>
           <t>Kapasite</t>
         </is>
       </c>
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>10 m³/saat @ 8,1 mSS</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="18" customHeight="1">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Motor</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="inlineStr">
-        <is>
-          <t>0.8 kW</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>Tip</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="inlineStr">
-        <is>
-          <t>Santrifüj Tip</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="24" customHeight="1">
-      <c r="A65" s="1" t="inlineStr">
-        <is>
-          <t>İNŞAAT İŞLERİ</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="n"/>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>Izgara Kanalı</t>
-        </is>
-      </c>
-      <c r="B67" s="4" t="n"/>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>3 m³ ıslak hacim</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="18" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>Malzeme</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>Betonarme</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="18" customHeight="1">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Bekleme Süresi</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>6,3 m³/sa pik debide 30 dakika</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Birinci Çöktürme Tankı</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="n"/>
+    </row>
+    <row r="72" ht="18" customHeight="1">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>1 Adet</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="18" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="73" ht="18" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>Kapasite</t>
         </is>
       </c>
-      <c r="B69" s="8" t="inlineStr">
-        <is>
-          <t>3 m³ ıslak hacim</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="18" customHeight="1">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>Malzeme</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>Betonarme</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="9" t="inlineStr">
-        <is>
-          <t>Bekleme Süresi</t>
-        </is>
-      </c>
-      <c r="B71" s="10" t="inlineStr">
-        <is>
-          <t>5,8 m³/sa pik debide 30 dakika</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>Birinci Çöktürme Tankı</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="n"/>
+      <c r="B73" s="8" t="inlineStr">
+        <is>
+          <t>16 m³ ıslak hacim</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="18" customHeight="1">
       <c r="A74" s="5" t="inlineStr">
         <is>
+          <t>Malzeme</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>Betonarme</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="18" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Bekleme Süresi</t>
+        </is>
+      </c>
+      <c r="B75" s="10" t="inlineStr">
+        <is>
+          <t>6,3 m³/sa pik debide 2,5 saat</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>İkinci Çöktürme Tankı</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>1 Adet</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="18" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
+    <row r="79" ht="18" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
         <is>
           <t>Kapasite</t>
         </is>
       </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>15 m³ ıslak hacim</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>Malzeme</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>Betonarme</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="18" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>Bekleme Süresi</t>
-        </is>
-      </c>
-      <c r="B77" s="10" t="inlineStr">
-        <is>
-          <t>5,8 m³/sa pik debide 2,5 saat</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="20" customHeight="1">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>İkinci Çöktürme Tankı</t>
-        </is>
-      </c>
-      <c r="B79" s="4" t="n"/>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>13 m³ ıslak hacim</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="18" customHeight="1">
       <c r="A80" s="5" t="inlineStr">
         <is>
+          <t>Malzeme</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>Betonarme</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="18" customHeight="1">
+      <c r="A81" s="9" t="inlineStr">
+        <is>
+          <t>Bekleme Süresi</t>
+        </is>
+      </c>
+      <c r="B81" s="10" t="inlineStr">
+        <is>
+          <t>6,3 m³/sa pik debide 2 saat</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>Dengeleme Tankı</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="n"/>
+    </row>
+    <row r="84" ht="18" customHeight="1">
+      <c r="A84" s="5" t="inlineStr">
+        <is>
           <t>Miktar</t>
         </is>
       </c>
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>1 Adet</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="18" customHeight="1">
-      <c r="A81" s="7" t="inlineStr">
+    <row r="85" ht="18" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>Kapasite</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>12 m³ ıslak hacim</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>Malzeme</t>
-        </is>
-      </c>
-      <c r="B82" s="6" t="inlineStr">
-        <is>
-          <t>Betonarme</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="18" customHeight="1">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>Bekleme Süresi</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>5,8 m³/sa pik debide 2 saat</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>Dengeleme Tankı</t>
-        </is>
-      </c>
-      <c r="B85" s="4" t="n"/>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>13 m³ ıslak hacim</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="18" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>Miktar</t>
+          <t>Malzeme</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>1 Adet</t>
+          <t>Betonarme</t>
         </is>
       </c>
     </row>
     <row r="87" ht="18" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>Kapasite</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="inlineStr">
-        <is>
-          <t>12 m³ ıslak hacim</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="18" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>Malzeme</t>
-        </is>
-      </c>
-      <c r="B88" s="6" t="inlineStr">
-        <is>
-          <t>Betonarme</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="18" customHeight="1">
-      <c r="A89" s="9" t="inlineStr">
+      <c r="A87" s="9" t="inlineStr">
         <is>
           <t>Bekleme Süresi</t>
         </is>
       </c>
-      <c r="B89" s="10" t="inlineStr">
-        <is>
-          <t>5,8 m³/sa pik debide 2 saat</t>
+      <c r="B87" s="10" t="inlineStr">
+        <is>
+          <t>6,3 m³/sa pik debide 2 saat</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
+    <mergeCell ref="A48:B48"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A79:B79"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A71:B71"/>
+    <mergeCell ref="A63:B63"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A46:B46"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A67:B67"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A83:B83"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
